--- a/exports/qa-admin-chats-export.xlsx
+++ b/exports/qa-admin-chats-export.xlsx
@@ -30,12 +30,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,7 +55,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -61,6 +66,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,16 +435,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,189 +477,53 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>反馈描述</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>每轮对话生成的sql语句</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>对话时间</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>吴东洋</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>平台录入认证企业清单</t>
+          <t>生效租户数量</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>提取25年6月之前认证方式是平台录入 建档的企业清单</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>SELECT cust_no AS 客户编号,
-       name AS 客户名称,
-       certification_no AS 统一信用代码,
-       identify_style AS 认证方式,
-       cust_build_type AS 录入方式,
-       cust_build_status AS 认证状态,
-       create_time AS 建档时间
-FROM cust_company_info
-WHERE NOT identify_style IN ('INVITE',
-                             'INVITE_AGW',
-                             'SIMPLE')
-  AND NOT identify_style IS NULL
-  AND create_time &lt; '2025-06-01 00:00:00'
-ORDER BY create_time DESC
-LIMIT 1000
-SELECT cust_no AS 客户编号,
-       name AS 客户名称,
-       certification_no AS 统一信用代码,
-       identify_style AS 认证方式,
-       cust_build_type AS 录入方式,
-       cust_build_status AS 认证状态,
-       cust_source AS 建档数据来源,
-       create_time AS 建档时间
-FROM cust_company_info
-WHERE identify_style = 'INVITE_AGW'
-  AND create_time &lt; '2025-06-01 00:00:00'
-ORDER BY create_time DESC
-LIMIT 1000</t>
-        </is>
-      </c>
+          <t>查询生效的租户有多少个</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11 16:44:45.537</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>25年6月前邀请认证-内管录入企业清单</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>提取25年6月之前认证方式是平台录入 建档的企业清单</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>SELECT name AS 企业名称,
-       certification_no AS 统一社会信用代码,
-       identify_style AS 认证方式,
-       cust_build_type AS 录入方式,
-       cust_build_status AS 认证状态,
-       create_time AS 建档时间
-FROM cust_company_info
-WHERE identify_style = 'INVITE_AGW'
-  AND create_time &lt; '2025-06-01 00:00:00'
-ORDER BY create_time DESC</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11 16:45:21.641</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>平台录入认证企业清单（25年6月前建档）</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>提取25年6月之前认证方式是平台录入 建档的企业清单</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>SELECT code AS 客户编号,
-       name AS 企业名称,
-       identify_style AS 认证方式,
-       cust_build_type AS 录入方式,
-       cust_build_status AS 认证状态,
-       create_time AS 建档时间,
-       cert_no_flag AS 标识,
-       certification_no AS 统一信用代码
-FROM cust_company_info
-WHERE identify_style = 'INVITE_AGW'
-  AND create_time &lt; '2025-06-01 00:00:00'
-ORDER BY create_time DESC
-LIMIT 1000</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11 17:38:22.693</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>吴东洋</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>生效租户数量</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>查询生效的租户有多少个</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>赞</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS 生效租户数
 FROM tenant_setting_config
@@ -656,23 +531,25 @@
   AND status = 'Y'</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2026-09-11 17:52:20.162</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>统计每个租户开通了那些产品</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>SELECT t.name AS 租户名称,
        GROUP_CONCAT(DISTINCT p.name
@@ -685,23 +562,25 @@
 ORDER BY t.name</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>2026-09-11 17:54:22.572</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="I3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>每个租户运营配置项</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>SELECT t.name AS 租户名称,
        t.platform_operator AS 平台运营方,
@@ -717,23 +596,25 @@
 ORDER BY t.name</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:16:03.955</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="I4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>请分析上一条查询结果</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>SELECT COALESCE(NULLIF(platform_operator, ''), '未设置') AS 平台运营方,
        COUNT(*) AS 租户数,
@@ -773,17 +654,18 @@
 ORDER BY 租户数 DESC</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:17:39.794</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>1. 开启智能客服
 2. 智能客服系统号
@@ -803,12 +685,13 @@
 3. 默认关联的项目   租户运营配置项</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>赞</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>SELECT name AS 租户名称,
        operator_ai_customer AS 开启智能客服,
@@ -830,35 +713,37 @@
 FROM tenant_setting_config</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:48:58.446</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>刘宁</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>未登记银行账号的金融机构</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>查询银行账户为空的金融机构</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>SELECT c.cust_no AS 客户编号,
        c.name AS 客户名称,
@@ -881,23 +766,25 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>2026-09-11 18:03:28.060</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>查询银行账号=0的金融机构</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>SELECT c.cust_no AS 客户编号,
        c.name AS 客户名称,
@@ -920,23 +807,25 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>2026-09-11 18:05:16.753</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="I8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>查询银行账号为空的金融机构</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>SELECT c.cust_no AS 客户编号,
        c.name AS 客户名称,
@@ -959,163 +848,37 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:49:18.360</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>账号为空的银行账户所属企业角色分布</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>查询银行账户为空的金融机构</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>SELECT c.cust_company_type AS 企业角色,
-       COUNT(*) AS 账号为空的账户数
-FROM cust_account_info AS a
-LEFT JOIN cust_company_info AS c ON a.ref_cust_company_info = c.code
-WHERE a.account_no IS NULL
-  OR TRIM(a.account_no) = ''
-GROUP BY c.cust_company_type
-ORDER BY 账号为空的账户数 DESC
-LIMIT 1000</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11 18:21:26.978</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>银行关键信息缺失的金融机构账户</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>查询银行账户为空的金融机构</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>SELECT cc.code AS 企业编码,
-       cc.name AS 企业名称,
-       cc.finance_org_flag AS 金融机构身份标识,
-       cc.finance_org_type_name AS 金融机构类型,
-       ca.account_name AS 账户名称,
-       ca.account_no AS 账户账号,
-       ca.bank_no AS 联行号,
-       ca.bank_code_name AS 银行总行名称
-FROM cust_company_info AS cc
-JOIN cust_account_info AS ca ON ca.ref_cust_company_info = cc.code
-WHERE NOT cc.finance_org_flag IS NULL
-  AND cc.finance_org_flag &lt;&gt; ''
-  AND (ca.account_no IS NULL
-       OR ca.account_no = '')
-ORDER BY cc.code
-LIMIT 1000</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11 18:48:15.188</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>我要查询的是有帐户名称，但是账户帐号为空或0的</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>SELECT cc.code AS 企业编码,
-       cc.name AS 企业名称,
-       cc.finance_org_flag AS 金融机构身份标识,
-       cc.finance_org_type_name AS 金融机构类型,
-       ca.account_name AS 账户名称,
-       ca.account_no AS 账户账号,
-       ca.bank_no AS 联行号,
-       ca.bank_code_name AS 银行总行名称
-FROM cust_company_info AS cc
-JOIN cust_account_info AS ca ON ca.ref_cust_company_info = cc.code
-WHERE NOT cc.finance_org_flag IS NULL
-  AND cc.finance_org_flag &lt;&gt; ''
-  AND NOT ca.account_name IS NULL
-  AND ca.account_name &lt;&gt; ''
-  AND (ca.account_no IS NULL
-       OR ca.account_no = ''
-       OR ca.account_no = '0')
-ORDER BY cc.code
-LIMIT 1000</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11 18:51:38.112</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>刘宁</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>银行账号为空的核心企业清单</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>查询银行账号为空的核心企业</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>SELECT c.code AS 企业编码,
        c.name AS 企业名称,
@@ -1134,27 +897,29 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:50:42.917</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>只需要检查认证成功的企业数据</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>赞</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>SELECT c.code AS 企业编码,
        c.name AS 企业名称,
@@ -1174,23 +939,25 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:52:05.867</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="I11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>查询银行账号为空的认证成功的金融机构</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>SELECT c.code AS 企业编码,
        c.name AS 企业名称,
@@ -1210,35 +977,37 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:53:01.773</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>吴东洋</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>LN1租户已生效企业关联项目及开通状态</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>查询LN1租户下的  已经生效的企业  关联的项目  已经项目开通状态</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>SELECT c.name AS 企业名称,
        c.cust_status AS 企业状态,
@@ -1253,23 +1022,25 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:53:29.136</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>请分析上一条查询结果</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>SELECT p.project_open_status AS 项目开通状态,
        COUNT(DISTINCT c.code) AS 企业数,
@@ -1283,23 +1054,25 @@
 ORDER BY 企业项目关联记录数 DESC</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:55:30.210</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="I14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>请基于上一条查询结果进行预测</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>SELECT DATE_FORMAT(p.create_time, '%Y-%m') AS 月份,
        p.project_open_status AS 项目开通状态,
@@ -1338,35 +1111,159 @@
 ORDER BY 1</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>2026-09-12 10:55:59.775</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>关联联塑项目的企业建档注册状态，以及项目开通状态</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>没有理解对项目</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>SELECT CASE c.cust_build_status
+           WHEN 'INIT' THEN '初始化'
+           WHEN 'CUST_CONFIRM_AWAIT' THEN '待客户确认'
+           WHEN 'AWAIT_CUST_CONFIRM' THEN '待客户确认'
+           WHEN 'CUST_BUILDING' THEN '审批中'
+           WHEN 'BUILDING' THEN '建档中'
+           WHEN 'BUILD_BACK' THEN '退回'
+           WHEN 'BUILD_FAIL' THEN '认证失败'
+           WHEN 'BUILD_SUCCESS' THEN '认证成功'
+           WHEN 'BUILD_ACTIVATE' THEN '待激活'
+           WHEN 'TO_BE_BUILD' THEN '未建档'
+           WHEN 'CUST_AUDIT_AWAIT' THEN '待审核'
+           WHEN 'CUST_BUILD_SUCCESS' THEN '审核通过'
+           WHEN 'CUST_BUILD_FAIL' THEN '审核拒绝'
+           WHEN 'CUST_CHANGE' THEN '变更'
+           ELSE c.cust_build_status
+       END AS 企业建档注册状态,
+       CASE p.project_open_status
+           WHEN 'OPENED' THEN '已开通'
+           WHEN 'NOT_OPEN' THEN '未开通'
+           ELSE p.project_open_status
+       END AS 项目开通状态,
+       COUNT(DISTINCT c.code) AS 企业数,
+       COUNT(DISTINCT p.project_id) AS 项目数,
+       COUNT(*) AS 企业项目关联记录数
+FROM cust_company_info AS c
+JOIN cust_project_rel AS p ON p.ref_cust_project_rel_cust_company_info = c.code
+WHERE p.tenant_code = 'LN1'
+GROUP BY c.cust_build_status,
+         p.project_open_status
+ORDER BY 3 DESC</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:59:19.918</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>项目名称 不是租户名称</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>SELECT CASE c.cust_build_status
+           WHEN 'INIT' THEN '初始化'
+           WHEN 'CUST_CONFIRM_AWAIT' THEN '待客户确认'
+           WHEN 'AWAIT_CUST_CONFIRM' THEN '待客户确认'
+           WHEN 'CUST_BUILDING' THEN '审批中'
+           WHEN 'BUILDING' THEN '建档中'
+           WHEN 'BUILD_BACK' THEN '退回'
+           WHEN 'BUILD_FAIL' THEN '认证失败'
+           WHEN 'BUILD_SUCCESS' THEN '认证成功'
+           WHEN 'BUILD_ACTIVATE' THEN '待激活'
+           WHEN 'TO_BE_BUILD' THEN '未建档'
+           WHEN 'CUST_AUDIT_AWAIT' THEN '待审核'
+           WHEN 'CUST_BUILD_SUCCESS' THEN '审核通过'
+           WHEN 'CUST_BUILD_FAIL' THEN '审核拒绝'
+           WHEN 'CUST_CHANGE' THEN '变更'
+           ELSE c.cust_build_status
+       END AS 企业建档注册状态,
+       CASE p.project_open_status
+           WHEN 'OPENED' THEN '已开通'
+           WHEN 'NOT_OPEN' THEN '未开通'
+           ELSE p.project_open_status
+       END AS 项目开通状态,
+       COUNT(DISTINCT c.code) AS 企业数,
+       COUNT(DISTINCT p.project_id) AS 项目数,
+       COUNT(*) AS 企业项目关联记录数
+FROM cust_company_info AS c
+JOIN cust_project_rel AS p ON p.ref_cust_project_rel_cust_company_info = c.code
+WHERE p.name = '联塑项目'
+GROUP BY c.cust_build_status,
+         p.project_open_status
+ORDER BY 3 DESC</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:03:01.863</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>欧阳鹏飞</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>项目运营配置清单</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>导出项目运营配置数据包括项目ID	项目名称	项目标识	项目归属	渠道	产品类型	项目状态	是否生产数据	企微审批编号/立项审批编号	项目立项审批通过时间	项目码	运营对接人A	运营对接人B	运营组别	查验对接人	查验组别	风控对接人A	风控对接人B	风控组别	方案经理	业务经理	关联业务部门	项目创建时间	项目配置提交时间	首笔落地时间	更新人	更新时间	自定义字段一	自定义字段二	自定义字段三	项目标签	运营项目归属	置顶标识	客服话术</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>数据库是对的，但导出的对应中文无法关联处理，这种可能是代码里面没有完整的枚举那种数据 ， 像其中的产品 运营人员只显示id</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>SELECT tp.id AS `项目ID`,
        tp.name AS `项目名称`,
@@ -1417,69 +1314,131 @@
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>2026-09-14 10:11:50.272</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>导出龙腾建档项目关联企业的所有用户</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT tp.name AS `项目名称`,
+                cpr.ref_cust_project_rel_cust_company_info AS `关联企业编码`,
+                ci.name AS `关联企业名称`,
+                cpr.company_type AS `关联企业角色`,
+                cpi.code AS `用户编码`,
+                CASE cpi.user_type
+                    WHEN 'accountAdmin' THEN '管理员'
+                    WHEN 'accountNormal' THEN '经办人'
+                    WHEN 'accountGuest' THEN '游客'
+                    ELSE cpi.user_type
+                END AS `用户角色`,
+                CASE cpi.status
+                    WHEN 'ADD' THEN '未生效'
+                    WHEN 'EFFECT' THEN '已生效'
+                    WHEN 'FREEZE' THEN '冻结'
+                    ELSE cpi.status
+                END AS `账号状态`,
+                cpi.cust_build_status AS `建档状态`,
+                cpi.skip_auth_flag AS `跳过实名认证`,
+                cpi.test_data AS `测试数据`,
+                cpi.create_time AS `创建时间`
+FROM tenant_project AS tp
+JOIN cust_project_rel AS cpr ON cpr.project_id = tp.id
+AND cpr.enable = 'Y'
+JOIN cust_company_info AS ci ON ci.code = cpr.ref_cust_project_rel_cust_company_info
+JOIN cust_person_info AS cpi ON cpi.ref_cust_company_info = ci.code
+WHERE tp.name = '龙腾建档项目'
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:52:41.580</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>CA服务费的订单分析下有哪些成功了</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>SELECT fo.order_no AS `订单号`,
+       fo.company_name AS `企业名称`,
+       fo.certification_no AS `统一社会信用代码`,
+       fo.company_type AS `企业角色`,
+       fo.project_name AS `触发项目`,
+       fo.order_type AS `订单类型`,
+       fo.pay_amount AS `实缴金额(元)`,
+       fo.service_start AS `服务周期起始`,
+       fo.service_end AS `服务周期截止`,
+       fo.pay_time AS `缴费成功时间`
+FROM ca_fee_order AS fo
+WHERE fo.order_status = 'PAID'
+ORDER BY fo.pay_time DESC
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:07:46.925</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>王合庆</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>各租户开通产品清单</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>我能做什么</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:54:36.553</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>有哪些数据可以供我查询使用</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:55:14.301</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>统计每个租户开通了哪些产品</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>SELECT t.name AS tenant_name,
        t.db_tenant_code,
@@ -1494,11 +1453,191 @@
          tenant_name</t>
         </is>
       </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:55:47.364</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>未生成SQL的提问：
+1. 我能做什么
+2. 有哪些数据可以供我查询使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>刘宁</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>刘宁的项目立项审批状态统计</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>请查询方案经理=刘宁的项目立项统计数据</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>数量没对上，和页面查询的数据不一致</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>SELECT t.wf_status AS 审批状态,
+       CASE t.wf_status
+           WHEN 'PENDING' THEN '待发起'
+           WHEN 'RUNNING' THEN '审批中'
+           WHEN 'FINISHED' THEN '审批通过'
+           WHEN 'TERMINATED' THEN '审批拒绝'
+           ELSE t.wf_status
+       END AS 状态含义,
+       COUNT(*) AS 立项审批数量
+FROM tenant_project_approval AS t
+WHERE t.solution_manager_name LIKE '%刘宁%'
+GROUP BY t.wf_status
+ORDER BY 立项审批数量 DESC</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 20:13:14.604</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>未生成SQL的提问：
+林的供应商变更后，这个企业在列表中吗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>查询已生效的租户</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>SELECT t.name AS 租户名称,
+       t.code AS 编码,
+       t.app_tenant_code AS 逻辑租户标识,
+       t.tenant_flag_zh AS 项目标识,
+       t.status AS 生效状态,
+       t.enable AS 启用标记
+FROM tenant_setting_config AS t
+WHERE t.enable = 'Y'
+  AND t.status = 'Y'
+ORDER BY t.name</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 20:18:29.471</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>查询一下CA收费状态=已缴费的企业</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>SELECT c.company_name AS 企业名称,
+       c.code AS 编码,
+       CASE c.pay_status
+           WHEN 'PAID' THEN '已缴费'
+           WHEN 'UNPAID' THEN '未缴费'
+           ELSE c.pay_status
+       END AS 缴费状态,
+       c.service_start AS 服务周期起,
+       c.service_end AS 服务周期止
+FROM ca_fee_company AS c
+WHERE c.pay_status = 'PAID'
+ORDER BY c.company_name</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 20:22:49.397</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>刘宁</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>已生效租户清单</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>查询已生效租户</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 13:55:47.364</t>
-        </is>
-      </c>
+          <t>SELECT name AS 租户名称,
+       code AS 租户编码,
+       db_tenant_code AS 数据租户标识,
+       app_tenant_code AS 逻辑租户标识,
+       source AS 租户来源
+FROM tenant_setting_config
+WHERE enable = 'Y'
+  AND status = 'Y'
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17 20:32:20.630</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1508,115 +1647,681 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 17:23:06</t>
+          <t>已开通CA服务费的项目清单</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>查询关联了LN1项目的金融机构有哪些，分别是哪些贴牌下的</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
+          <t>哪些项目开通了CA服务费开关</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>不对，我通过数据库查出来的项目数量是44，但是问数平台的项目是41，查询sql不太对</t>
+        </is>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 17:23:39.493</t>
+          <t>SELECT c.source_project_id AS project_id,
+       MAX(o.project_name) AS project_name
+FROM ca_fee_company AS c
+LEFT JOIN ca_fee_order AS o ON o.project_id = c.source_project_id
+GROUP BY c.source_project_id
+ORDER BY c.source_project_id
+SELECT c.source_project_id AS project_id,
+       MAX(o.project_name) AS project_name
+FROM ca_fee_company AS c
+LEFT JOIN ca_fee_order AS o ON o.project_id = c.source_project_id
+WHERE NOT c.source_project_id IS NULL
+GROUP BY c.source_project_id
+ORDER BY c.source_project_id</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:42:26.574</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>未生成SQL的提问：
+提供一下是生产项目的项目数据</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>项目运营配置数据清单</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>导出项目运营配置数据包括项目ID	项目名称	项目标识	项目归属	渠道	产品类型	项目状态	是否生产数据	企微审批编号/立项审批编号	项目立项审批通过时间	项目码	运营对接人A	运营对接人B	运营组别	查验对接人	查验组别	风控对接人A	风控对接人B	风控组别	方案经理	业务经理	关联业务部门	项目创建时间	项目配置提交时间	首笔落地时间	更新人	更新时间	自定义字段一	自定义字段二	自定义字段三	项目标签	运营项目归属	置顶标识	客服话术</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr"/>
+          <t>哪些企业有CA服务费缴费待办，但是还没有缴费</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>SELECT id AS 项目ID,
-       name AS 项目名称,
-       tenant_flg_en AS 项目标识,
-       project_relation AS 项目归属,
-       channel_code AS 渠道,
-       platform_product_code AS 产品类型,
-       project_status AS 项目状态,
-       is_prd AS 是否生产数据,
-       wechat_audit_no AS 企微审批编号_立项审批编号,
-       wechat_audit_pass_time AS 项目立项审批通过时间,
-       channel_code AS 项目码,
-       op_contact_a AS 运营对接人A,
-       op_contact_b AS 运营对接人B,
-       op_contact_a_group AS 运营组别,
-       verification_contact AS 查验对接人,
-       verification_contact_group AS 查验组别,
-       risk_control_contact_a AS 风控对接人A,
-       risk_control_contact_b AS 风控对接人B,
-       risk_control_contact_a_group AS 风控组别,
-       solution_manager AS 方案经理,
-       business_manager AS 业务经理,
-       business_group AS 关联业务部门,
-       project_create_time AS 项目创建时间,
-       op_update_time AS 项目配置提交时间,
-       first_settlement_time AS 首笔落地时间,
-       update_user AS 更新人,
-       update_time AS 更新时间,
-       custom_field_one AS 自定义字段一,
-       custom_field_two AS 自定义字段二,
-       custom_field_three AS 自定义字段三,
-       project_tag AS 项目标签,
-       bussiness_project_relation AS 运营项目归属,
-       top_flag AS 置顶标识,
-       invite_customer_service_words AS 客服话术
+          <t>缴费待办在另一个库，该问题超纲，可以忽略不计</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>SELECT code AS 企业编码,
+       company_name AS 企业名称,
+       source_project_id AS 来源项目ID,
+       service_start AS 服务周期起始日,
+       service_end AS 服务周期截止日,
+       pay_status AS 缴费状态
+FROM ca_fee_company
+WHERE renew_remind_sent = 'Y'
+  AND pay_status = 'UNPAID'
+ORDER BY company_name
+SELECT company_name AS 企业名称,
+       source_company_type AS 企业角色,
+       source_project_id AS 来源项目ID,
+       service_start AS 服务周期起始日,
+       service_end AS 服务周期截止日
+FROM ca_fee_company
+WHERE renew_remind_sent = 'Y'
+  AND pay_status = 'UNPAID'
+ORDER BY service_end,
+         company_name</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:54:04.738</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>黄丽玉</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>运营人员为空且企业建档成功的联系人</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>请查询企业联系人维护中运营人员为空，且企业建档成功的数据</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>SELECT p.code AS 联系人编码,
+       CASE p.user_type
+           WHEN 'accountAdmin' THEN '管理员'
+           WHEN 'accountNormal' THEN '经办人'
+           WHEN 'accountGuest' THEN '游客'
+           ELSE p.user_type
+       END AS 联系人类型,
+       p.operator AS 运营人,
+       p.operator_realname AS 运营人姓名,
+       p.cust_company_id AS 企业ID,
+       p.ref_cust_company_info AS 关联企业编码,
+       c.cust_short_name AS 企业简称,
+       c.cust_build_status AS 企业建档状态
+FROM cust_person_info AS p
+JOIN cust_company_info AS c ON p.ref_cust_company_info = c.code
+WHERE (p.operator IS NULL
+       OR p.operator = '')
+  AND c.cust_build_status = 'BUILD_SUCCESS'
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:05:11.150</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>刘宁</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>生产项目清单</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>提供一下是生产项目的项目数据</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>SELECT id,
+       code,
+       project_code,
+       tenant_flg_en,
+       project_status,
+       project_tag,
+       config_model,
+       project_create_time,
+       project_effective_time,
+       enable
 FROM tenant_project
+WHERE is_prd = 'Y'
 LIMIT 1000</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:28:13.720</t>
-        </is>
-      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:09:24.424</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>刘宁</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>未关联企业的项目信息</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>提供一下没有关联企业的项目信息</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>SELECT tp.project_code AS 项目编码,
+       tp.tenant_flg_en AS 项目标识,
+       tp.project_status AS 项目状态,
+       tp.project_create_time AS 项目创建时间,
+       tp.op_update_user AS 运营信息更新人
+FROM tenant_project AS tp
+WHERE NOT EXISTS
+    (SELECT 1
+     FROM cust_project_rel AS r
+     WHERE r.project_id = tp.code)
+ORDER BY tp.project_create_time DESC
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:13:14.181</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>怎么没有项目名称</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>供票QA项目有关联企业</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>SELECT tp.name AS 项目名称,
+       tp.project_code AS 项目编码,
+       tp.tenant_flg_en AS 项目标识,
+       tp.project_status AS 项目状态,
+       tp.project_create_time AS 项目创建时间,
+       tp.op_update_user AS 运营信息更新人
+FROM tenant_project AS tp
+WHERE NOT EXISTS
+    (SELECT 1
+     FROM cust_project_rel AS r
+     WHERE r.project_id = tp.code)
+ORDER BY tp.project_create_time DESC
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:16:13.615</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>哪些企业运营人员为空</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>只有企业联系人编码，用户无法知道是哪个企业联系人，需要提供企业联系人对应的企业名称，企业角色，关联租户</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>SELECT c.name AS 企业名称,
+       c.code AS 企业编码,
+       p.user_type AS 联系人类型,
+       p.code AS 联系人编码,
+       p.operator AS 运营人,
+       p.operator_id AS 运营人ID
+FROM cust_person_info AS p
+LEFT JOIN cust_company_info AS c ON c.code = p.ref_cust_company_info
+WHERE (p.operator IS NULL
+       OR p.operator = '')
+ORDER BY c.name
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:45:17.783</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>薛梦冉</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>变更中且已开通融易单的企业及管理员联系方</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>变更中且已开通融易单的企业 + 管理员联系方式</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT c.code AS 企业编码,
+                c.cust_short_name AS 企业简称,
+                p.name AS 管理员姓名,
+                p.phone AS 手机号,
+                p.email AS 邮箱,
+                p.enable AS 管理员启用状态
+FROM cust_auth_application AS a
+JOIN cust_company_info AS c ON a.ref_parent_company = c.code
+JOIN cust_person_info AS p ON p.ref_cust_company_info = c.code
+AND p.user_type = 'accountAdmin'
+WHERE c.cust_status = 'CHANGE'
+  AND a.name = '融易单'
+  AND a.open_status = 'OPENED'
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:25:42.703</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>各租户融易单(ACFLOW) 开通状态分布</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>SELECT CASE tp.open_status
+           WHEN 'Y' THEN '已开通'
+           WHEN 'P' THEN '开通中'
+           WHEN 'N' THEN '未开通'
+           ELSE tp.open_status
+       END AS 开通状态,
+       COUNT(*) AS 租户数
+FROM tenant_product AS tp
+WHERE tp.platform_product_code = 'ACFLOW'
+GROUP BY tp.open_status
+ORDER BY 租户数 DESC</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:28:14.514</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>CA 收费「已签协议未缴费」</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>SELECT db_tenant_code AS 数据租户标识,
+       tenant_id AS 租户ID,
+       project_id AS 触发项目ID,
+       agreement_signed AS 是否已签署收费协议,
+       agreement_sign_time AS 协议签署时间,
+       order_status AS 订单状态,
+       invoice_status AS 发票状态,
+       pay_time AS 缴费成功时间
+FROM ca_fee_order
+WHERE agreement_signed = 'Y'
+  AND order_status = 'PENDING'
+ORDER BY agreement_sign_time DESC</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:43:18.258</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>CA 已注册的企业里，有多少生成了待缴订单、签了多少协议、最终多少已缴费</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>认同</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(DISTINCT c.code) AS 已注册企业数,
+       COUNT(DISTINCT CASE
+                          WHEN o.order_status = 'PENDING' THEN c.code
+                      END) AS 生成待缴订单企业数,
+       COUNT(DISTINCT CASE
+                          WHEN o.agreement_signed = 'Y' THEN c.code
+                      END) AS 已签收费协议企业数,
+       COUNT(DISTINCT CASE
+                          WHEN c.pay_status = 'PAID' THEN c.code
+                      END) AS 已缴费企业数
+FROM ca_fee_company AS c
+LEFT JOIN ca_fee_order AS o ON o.project_id = c.source_project_id
+SELECT COUNT(DISTINCT c.company_name) AS 已注册企业数,
+       COUNT(DISTINCT CASE
+                          WHEN o.order_status = 'PENDING' THEN c.company_name
+                      END) AS 生成待缴订单企业数,
+       COUNT(DISTINCT CASE
+                          WHEN o.agreement_signed = 'Y' THEN c.company_name
+                      END) AS 已签收费协议企业数,
+       COUNT(DISTINCT CASE
+                          WHEN c.pay_status = 'PAID' THEN c.company_name
+                      END) AS 已缴费企业数
+FROM ca_fee_company AS c
+LEFT JOIN ca_fee_order AS o ON o.project_id = c.source_project_id</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:56:01.953</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>刘倍材</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>项目上线审批明细</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>帮忙统计发起时间从9.1到9.18的项目上线审批数据，列出项目名称	立项审批编号	审批编码	项目类型	是否发起审批	发起人	审批状态	审批发起时间	审批完成时间	审批节点	审批人员	审批结果	审批节点开始时间	审批节点结束时间</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>不认同</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>1、审批轨迹不是真实的数据，不包括转审的数据，如项目方案很长项目1（审批编号SX2026090300522）
+2、已经拒绝的审批，还将预定的后续节点的数据列出（如测试白名单验证0731-32，审批编号为SX2026073100406）：也是没有取真实的审批轨迹
+2、审批撤销没有转为中文</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>SELECT a.name AS 项目名称,
+       a.sp_no AS 立项审批编号,
+       a.approval_no AS 审批编码,
+       a.project_type AS 项目类型,
+       a.is_online_approval AS 是否发起审批,
+       a.initiator_user_name AS 发起人,
+       a.wf_status AS 审批状态,
+       a.initiate_time AS 审批发起时间,
+       a.complete_time AS 审批完成时间,
+       f.node_name AS 审批节点,
+       f.approver_user_name AS 审批人员,
+       f.node_status AS 审批结果,
+       f.create_time AS 审批节点开始时间,
+       f.update_time AS 审批节点结束时间
+FROM tenant_project_approval AS a
+JOIN tenant_project_approval_flow AS f ON a.code = f.ref_tenant_project_approval_flow_tenant_project_approval
+WHERE a.initiate_time &gt;= '2026-09-01 00:00:00'
+  AND a.initiate_time &lt;= '2026-09-18 23:59:59'
+ORDER BY a.initiate_time,
+         a.code,
+         f.node_order
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:02:44.254</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>在项目配置中已经删除了，但在项目审批中未删除的数据，列出ref_tenant_project_approval_tenant_project， 立项审批编号	审批编码	项目类型	是否发起审批	发起人	审批状态	审批发起时间	审批完成时间</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>SELECT a.ref_tenant_project_approval_tenant_project AS 关联租户项目,
+       a.sp_no AS 立项审批编号,
+       a.approval_no AS 审批编码,
+       a.project_type AS 项目类型,
+       a.is_online_approval AS 是否发起审批,
+       a.initiator_user_name AS 发起人,
+       a.wf_status AS 审批状态,
+       a.initiate_time AS 审批发起时间,
+       a.complete_time AS 审批完成时间
+FROM tenant_project_approval AS a
+LEFT JOIN tenant_project AS p ON p.code = a.ref_tenant_project_approval_tenant_project
+WHERE NOT a.ref_tenant_project_approval_tenant_project IS NULL
+  AND p.code IS NULL
+ORDER BY a.initiate_time
+LIMIT 1000</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:53:38.620</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>汇总：总对话数=14；对话轮次数=37；认同数=11；不认同数=8</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="A5:A9"/>
+  <mergeCells count="41">
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="I13:I17"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="I33:I36"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="I2:I6"/>
+    <mergeCell ref="I30:I32"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="I7:I9"/>
     <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A18:A20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1628,11 +2333,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1667,7 +2372,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1679,7 +2384,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1698,84 +2403,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>导出对话数</t>
+          <t>排除 Admin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>导出行数(轮次)</t>
+          <t>排除无SQL对话</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>聚合</t>
+          <t>导出对话数</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>按 chatid 分组；操作人名/chatid/对话brief 合并单元格</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>组内排序</t>
+          <t>导出行数(有SQL轮次)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>同一 chatid 内按对话时间升序</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SQL来源</t>
+          <t>认同数 / 不认同数</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>优先 record.sql；否则 answer.datasets[].sql</t>
+          <t>11 / 8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>反馈映射</t>
+          <t>聚合</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>up→赞，down→踩；附 feedback_comment</t>
+          <t>按 chatid 分组；操作人名/chatid/对话brief/备注 合并单元格</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>组内排序</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>优先使用该轮 create_time</t>
+          <t>同一 chatid 内按对话时间升序</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SQL过滤</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>整段对话无SQL则排除；有SQL时去掉无SQL轮次，提问写入备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>反馈映射</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>up→认同，down→不认同；反馈描述=feedback_comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>汇总行</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>总对话数 / 对话轮次数 / 认同数 / 不认同数</t>
         </is>
       </c>
     </row>
